--- a/data/asp_report.xlsx
+++ b/data/asp_report.xlsx
@@ -1002,7 +1002,7 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Biosimilar ASP Monitor — Samsung Bioepis Market Report 검증  |  Data: CMS Medicare Part B  |  생성: 2026-04-01 22:45</t>
+          <t>Biosimilar ASP Monitor — Samsung Bioepis Market Report 검증  |  Data: CMS Medicare Part B  |  생성: 2026-04-02 00:54</t>
         </is>
       </c>
     </row>

--- a/data/asp_report.xlsx
+++ b/data/asp_report.xlsx
@@ -1002,7 +1002,7 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Biosimilar ASP Monitor — Samsung Bioepis Market Report 검증  |  Data: CMS Medicare Part B  |  생성: 2026-04-02 00:54</t>
+          <t>Biosimilar ASP Monitor — Samsung Bioepis Market Report 검증  |  Data: CMS Medicare Part B  |  생성: 2026-04-02 01:04</t>
         </is>
       </c>
     </row>

--- a/data/asp_report.xlsx
+++ b/data/asp_report.xlsx
@@ -1002,7 +1002,7 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Biosimilar ASP Monitor — Samsung Bioepis Market Report 검증  |  Data: CMS Medicare Part B  |  생성: 2026-04-02 01:04</t>
+          <t>Biosimilar ASP Monitor — Samsung Bioepis Market Report 검증  |  Data: CMS Medicare Part B  |  생성: 2026-04-02 02:06</t>
         </is>
       </c>
     </row>

--- a/data/asp_report.xlsx
+++ b/data/asp_report.xlsx
@@ -1002,7 +1002,7 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Biosimilar ASP Monitor — Samsung Bioepis Market Report 검증  |  Data: CMS Medicare Part B  |  생성: 2026-04-02 02:06</t>
+          <t>Biosimilar ASP Monitor — Samsung Bioepis Market Report 검증  |  Data: CMS Medicare Part B  |  생성: 2026-04-02 02:11</t>
         </is>
       </c>
     </row>

--- a/data/asp_report.xlsx
+++ b/data/asp_report.xlsx
@@ -1002,7 +1002,7 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Biosimilar ASP Monitor — Samsung Bioepis Market Report 검증  |  Data: CMS Medicare Part B  |  생성: 2026-04-02 02:11</t>
+          <t>Biosimilar ASP Monitor — Samsung Bioepis Market Report 검증  |  Data: CMS Medicare Part B  |  생성: 2026-04-06 02:07</t>
         </is>
       </c>
     </row>
